--- a/data/trans_dic/P55$auxiliar-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P55$auxiliar-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda los Servicios Sociales cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda los Servicios Sociales cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,26</t>
+          <t>0,0; 36,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,82; 71,77</t>
+          <t>8,87; 63,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 25,17</t>
+          <t>2,7; 24,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,28; 45,21</t>
+          <t>12,04; 46,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,54; 45,96</t>
+          <t>9,09; 46,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,5; 44,93</t>
+          <t>21,75; 46,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,54; 36,47</t>
+          <t>10,59; 34,98</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,31; 45,25</t>
+          <t>13,4; 44,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,21; 31,61</t>
+          <t>15,08; 31,71</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,31</t>
+          <t>0,0; 29,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,27; 38,26</t>
+          <t>5,24; 38,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,26</t>
+          <t>0,0; 23,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,66; 32,44</t>
+          <t>7,88; 32,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,71</t>
+          <t>0,0; 18,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,78; 24,38</t>
+          <t>8,59; 23,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,36</t>
+          <t>0,0; 12,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,72; 25,6</t>
+          <t>7,07; 25,86</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,61</t>
+          <t>0,0; 11,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,85; 23,28</t>
+          <t>9,91; 23,94</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,77; 35,3</t>
+          <t>9,69; 36,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,93; 56,29</t>
+          <t>19,34; 56,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,8; 34,19</t>
+          <t>15,24; 32,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,59; 38,86</t>
+          <t>10,72; 39,4</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,33; 31,18</t>
+          <t>16,36; 30,68</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,72</t>
+          <t>0,0; 43,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,31; 57,39</t>
+          <t>20,28; 58,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 26,88</t>
+          <t>3,26; 26,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,98; 26,0</t>
+          <t>2,92; 24,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,84</t>
+          <t>0,0; 25,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,21; 37,62</t>
+          <t>20,27; 38,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 19,27</t>
+          <t>2,34; 19,12</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 17,1</t>
+          <t>2,0; 17,54</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 22,1</t>
+          <t>2,2; 22,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,65; 40,35</t>
+          <t>22,79; 39,49</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1287,52 +1287,52 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,52; 62,64</t>
+          <t>18,45; 67,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,3</t>
+          <t>0,0; 25,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,04; 40,65</t>
+          <t>7,89; 41,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,37</t>
+          <t>0,0; 30,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,46; 47,27</t>
+          <t>19,27; 46,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,12</t>
+          <t>0,0; 18,07</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,38; 43,53</t>
+          <t>12,47; 43,45</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,15</t>
+          <t>0,0; 23,55</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,24; 47,79</t>
+          <t>22,01; 46,7</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,03; 47,29</t>
+          <t>5,92; 47,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,21; 23,38</t>
+          <t>5,96; 23,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,67; 47,55</t>
+          <t>9,59; 44,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28,12; 47,72</t>
+          <t>27,68; 47,76</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10,77; 38,75</t>
+          <t>13,28; 39,98</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20,12; 34,32</t>
+          <t>20,15; 34,56</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,39</t>
+          <t>0,0; 17,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,99; 34,62</t>
+          <t>4,86; 36,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,61</t>
+          <t>0,0; 15,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,14; 25,77</t>
+          <t>4,37; 25,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,19; 18,83</t>
+          <t>2,16; 18,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,93; 36,22</t>
+          <t>17,21; 35,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,69</t>
+          <t>0,0; 9,27</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,27; 19,13</t>
+          <t>4,12; 18,83</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,46; 14,01</t>
+          <t>1,47; 12,82</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,54; 31,22</t>
+          <t>15,74; 30,78</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,81</t>
+          <t>0,0; 12,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,43</t>
+          <t>0,0; 16,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,42; 27,95</t>
+          <t>3,38; 27,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,92; 17,15</t>
+          <t>1,93; 18,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,55; 23,41</t>
+          <t>4,55; 23,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,22</t>
+          <t>0,0; 13,04</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,79; 25,9</t>
+          <t>11,03; 25,92</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,43; 11,58</t>
+          <t>1,42; 11,81</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,22; 17,96</t>
+          <t>3,11; 18,11</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,76</t>
+          <t>0,0; 8,8</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,38; 22,72</t>
+          <t>10,8; 22,9</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,64</t>
+          <t>0,0; 3,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,28; 14,05</t>
+          <t>4,21; 13,99</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,08; 9,95</t>
+          <t>2,01; 9,49</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13,98; 23,76</t>
+          <t>14,04; 24,15</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,87; 7,42</t>
+          <t>1,91; 7,67</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,99; 23,53</t>
+          <t>14,12; 23,98</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,77; 10,54</t>
+          <t>3,81; 10,86</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>21,26; 28,07</t>
+          <t>21,19; 28,1</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,62; 5,47</t>
+          <t>1,51; 5,32</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11,65; 19,03</t>
+          <t>11,57; 18,56</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3,86; 9,25</t>
+          <t>3,7; 8,66</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>19,86; 25,56</t>
+          <t>19,87; 25,45</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda los Servicios Sociales cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda los Servicios Sociales cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1624</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4742</t>
+          <t>0; 4307</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>793; 6458</t>
+          <t>798; 5687</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>740; 6804</t>
+          <t>730; 6534</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1919</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3208; 12857</t>
+          <t>3425; 13216</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2116; 11382</t>
+          <t>2252; 11484</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6745; 14782</t>
+          <t>7156; 15226</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1889</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4240; 14666</t>
+          <t>4259; 14067</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4495; 15277</t>
+          <t>4526; 15026</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9116; 18945</t>
+          <t>9035; 19006</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1926</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6659</t>
+          <t>0; 6919</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1605</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>811; 5885</t>
+          <t>806; 5886</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5282</t>
+          <t>0; 5301</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3242; 13733</t>
+          <t>3336; 13682</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 7527</t>
+          <t>0; 6618</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4827; 13410</t>
+          <t>4727; 12830</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4430</t>
+          <t>0; 4702</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5084; 16856</t>
+          <t>4653; 17029</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 6680</t>
+          <t>0; 5629</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6228; 16390</t>
+          <t>6979; 16851</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1634</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1942</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1472</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2765; 9066</t>
+          <t>2488; 9344</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1949</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5280; 14911</t>
+          <t>5123; 14928</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2184</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7034; 15225</t>
+          <t>6788; 14644</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 1918</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4332; 15889</t>
+          <t>4383; 16111</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 1854</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11465; 21890</t>
+          <t>11489; 21543</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1688</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 1924</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5544</t>
+          <t>0; 6102</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3360; 9496</t>
+          <t>3355; 9689</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1048; 8581</t>
+          <t>1040; 8540</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1178; 10263</t>
+          <t>1154; 9808</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 7593</t>
+          <t>0; 7372</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6899; 13514</t>
+          <t>7280; 13663</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1027; 8731</t>
+          <t>1062; 8661</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1120; 10046</t>
+          <t>1175; 10304</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1262; 9577</t>
+          <t>955; 9844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11881; 21172</t>
+          <t>11956; 20720</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1355</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3051,52 +3051,52 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1303</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1400; 5006</t>
+          <t>1475; 5361</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3951</t>
+          <t>0; 3953</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2031; 10269</t>
+          <t>1992; 10514</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 6855</t>
+          <t>0; 7251</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3140; 7628</t>
+          <t>3109; 7436</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4395</t>
+          <t>0; 4384</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4237; 14901</t>
+          <t>4269; 14874</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 7024</t>
+          <t>0; 6852</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5365; 11532</t>
+          <t>5312; 11269</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1706</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1091; 8550</t>
+          <t>1070; 8549</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1492</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1503; 5655</t>
+          <t>1443; 5722</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 2047</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2057; 10119</t>
+          <t>2041; 9480</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 2336</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8877; 15065</t>
+          <t>8738; 15076</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 1951</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4241; 15252</t>
+          <t>5229; 15739</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 1978</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11216; 19134</t>
+          <t>11235; 19268</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1693</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 5098</t>
+          <t>0; 4985</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 1799</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1392; 8047</t>
+          <t>1129; 8575</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 5722</t>
+          <t>0; 5985</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3030; 12720</t>
+          <t>2160; 12534</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1232; 10604</t>
+          <t>1216; 10489</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>9045; 19355</t>
+          <t>9197; 18966</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 6769</t>
+          <t>0; 5366</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3357; 15053</t>
+          <t>3245; 14819</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1212; 11597</t>
+          <t>1219; 10609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>11914; 23940</t>
+          <t>12072; 23603</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 3838</t>
+          <t>0; 4081</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2194</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 5053</t>
+          <t>0; 4186</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>582; 4753</t>
+          <t>575; 4726</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>912; 8155</t>
+          <t>919; 8824</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2133; 10977</t>
+          <t>2131; 11157</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 6801</t>
+          <t>0; 7259</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>6340; 15216</t>
+          <t>6483; 15232</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1144; 9275</t>
+          <t>1136; 9455</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2177; 12165</t>
+          <t>2104; 12263</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0; 7042</t>
+          <t>0; 7078</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>7861; 17212</t>
+          <t>8184; 17346</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0; 4607</t>
+          <t>0; 4547</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>6250; 20530</t>
+          <t>6158; 20445</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2529; 12082</t>
+          <t>2442; 11524</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>21961; 37320</t>
+          <t>22056; 37927</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>4324; 17142</t>
+          <t>4420; 17722</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>39099; 65787</t>
+          <t>39457; 67023</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10079; 28185</t>
+          <t>10177; 29027</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>69791; 92136</t>
+          <t>69568; 92229</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5776; 19551</t>
+          <t>5392; 19014</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>49579; 81000</t>
+          <t>49252; 79016</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>15005; 35978</t>
+          <t>14368; 33654</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>96364; 124046</t>
+          <t>96424; 123491</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P55$auxiliar-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P55$auxiliar-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>21,76%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,57</t>
+          <t>0,0; 41,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,87; 63,2</t>
+          <t>8,81; 71,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,7; 24,17</t>
+          <t>2,54; 22,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,17 +742,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,04; 46,48</t>
+          <t>11,46; 45,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,09; 46,37</t>
+          <t>8,87; 46,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,75; 46,29</t>
+          <t>20,74; 44,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,59; 34,98</t>
+          <t>10,11; 35,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,4; 44,5</t>
+          <t>14,11; 45,32</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,08; 31,71</t>
+          <t>15,12; 29,86</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>16,28%</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,42</t>
+          <t>0,0; 31,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,47 +872,47 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,24; 38,26</t>
+          <t>5,46; 39,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,34</t>
+          <t>0,0; 24,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,88; 32,32</t>
+          <t>8,01; 34,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,21</t>
+          <t>0,0; 17,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,59; 23,33</t>
+          <t>9,39; 24,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,06</t>
+          <t>0,0; 11,59</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,07; 25,86</t>
+          <t>7,99; 26,55</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,47</t>
+          <t>0,0; 11,38</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,91; 23,94</t>
+          <t>10,19; 23,92</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,69; 36,38</t>
+          <t>9,36; 33,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,34; 56,35</t>
+          <t>19,78; 56,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,24; 32,88</t>
+          <t>15,94; 33,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,72; 39,4</t>
+          <t>10,72; 39,33</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,36; 30,68</t>
+          <t>15,97; 30,61</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,44%</t>
         </is>
       </c>
     </row>
@@ -1147,52 +1147,52 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,72</t>
+          <t>0,0; 38,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,28; 58,56</t>
+          <t>20,07; 57,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,26; 26,76</t>
+          <t>3,34; 25,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,92; 24,85</t>
+          <t>2,97; 25,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,09</t>
+          <t>0,0; 27,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,27; 38,04</t>
+          <t>19,08; 37,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,34; 19,12</t>
+          <t>2,36; 18,84</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 17,54</t>
+          <t>2,01; 15,93</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 22,71</t>
+          <t>3,17; 25,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,79; 39,49</t>
+          <t>22,25; 39,93</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,33%</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,32; 75,89</t>
+          <t>12,43; 75,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,47 +1292,47 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,45; 67,07</t>
+          <t>12,6; 61,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,31</t>
+          <t>0,0; 31,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,89; 41,62</t>
+          <t>7,79; 40,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,01</t>
+          <t>0,0; 28,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,27; 46,08</t>
+          <t>19,98; 48,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,07</t>
+          <t>0,0; 17,32</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,47; 43,45</t>
+          <t>12,33; 43,46</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,55</t>
+          <t>0,0; 24,68</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,01; 46,7</t>
+          <t>21,1; 45,06</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,98%</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,92; 47,28</t>
+          <t>6,01; 53,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,96; 23,65</t>
+          <t>6,49; 23,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,59; 44,54</t>
+          <t>9,73; 48,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27,68; 47,76</t>
+          <t>28,12; 48,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13,28; 39,98</t>
+          <t>10,96; 40,36</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20,15; 34,56</t>
+          <t>20,98; 34,27</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,0</t>
+          <t>0,0; 16,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1572,47 +1572,47 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,86; 36,89</t>
+          <t>6,18; 36,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,28</t>
+          <t>0,0; 12,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,37; 25,39</t>
+          <t>5,86; 26,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,16; 18,62</t>
+          <t>2,2; 20,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17,21; 35,49</t>
+          <t>16,84; 34,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,27</t>
+          <t>0,0; 8,07</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,12; 18,83</t>
+          <t>4,08; 17,38</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 12,82</t>
+          <t>1,45; 13,68</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,74; 30,78</t>
+          <t>15,8; 30,8</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,3%</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,56</t>
+          <t>0,0; 13,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1707,52 +1707,52 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,92</t>
+          <t>0,0; 17,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,38; 27,8</t>
+          <t>3,33; 27,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,93; 18,55</t>
+          <t>1,9; 17,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,55; 23,79</t>
+          <t>4,52; 23,95</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,04</t>
+          <t>0,0; 10,85</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,03; 25,92</t>
+          <t>11,2; 26,87</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,42; 11,81</t>
+          <t>1,43; 12,37</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,11; 18,11</t>
+          <t>3,08; 16,45</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,8</t>
+          <t>0,0; 9,81</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,8; 22,9</t>
+          <t>10,39; 23,46</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,59</t>
+          <t>0,0; 3,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,21; 13,99</t>
+          <t>4,38; 13,59</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,01; 9,49</t>
+          <t>2,0; 9,63</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,04; 24,15</t>
+          <t>13,71; 23,67</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,91; 7,67</t>
+          <t>1,99; 7,38</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,12; 23,98</t>
+          <t>14,1; 23,8</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,81; 10,86</t>
+          <t>3,71; 10,81</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>21,19; 28,1</t>
+          <t>21,33; 27,47</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,51; 5,32</t>
+          <t>1,31; 5,09</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11,57; 18,56</t>
+          <t>11,78; 19,01</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3,7; 8,66</t>
+          <t>3,81; 9,16</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>19,87; 25,45</t>
+          <t>19,87; 25,28</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10679</t>
+          <t>10746</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13618</t>
+          <t>13670</t>
         </is>
       </c>
     </row>
@@ -2214,17 +2214,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4307</t>
+          <t>0; 4895</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>798; 5687</t>
+          <t>792; 6444</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>730; 6534</t>
+          <t>743; 6536</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2234,17 +2234,17 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3425; 13216</t>
+          <t>3258; 12970</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2252; 11484</t>
+          <t>2196; 11443</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7156; 15226</t>
+          <t>6967; 14945</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -2254,17 +2254,17 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4259; 14067</t>
+          <t>4068; 14096</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4526; 15026</t>
+          <t>4764; 15302</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9035; 19006</t>
+          <t>9498; 18757</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>2731</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8483</t>
+          <t>9480</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10971</t>
+          <t>12211</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6919</t>
+          <t>0; 7294</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2432,47 +2432,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>806; 5886</t>
+          <t>899; 6431</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5301</t>
+          <t>0; 5604</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3336; 13682</t>
+          <t>3393; 14570</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6618</t>
+          <t>0; 6256</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4727; 12830</t>
+          <t>5497; 14442</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4702</t>
+          <t>0; 4518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4653; 17029</t>
+          <t>5259; 17481</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5629</t>
+          <t>0; 5587</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6979; 16851</t>
+          <t>7639; 17944</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5386</t>
+          <t>5179</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10710</t>
+          <t>10567</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16096</t>
+          <t>15745</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2488; 9344</t>
+          <t>2361; 8524</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5123; 14928</t>
+          <t>5241; 14945</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6788; 14644</t>
+          <t>7109; 14732</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4383; 16111</t>
+          <t>4385; 16081</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11489; 21543</t>
+          <t>11150; 21372</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6087</t>
+          <t>6540</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9982</t>
+          <t>10429</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16069</t>
+          <t>16969</t>
         </is>
       </c>
     </row>
@@ -2843,52 +2843,52 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 6102</t>
+          <t>0; 5412</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3355; 9689</t>
+          <t>3564; 10156</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1040; 8540</t>
+          <t>1065; 8052</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1154; 9808</t>
+          <t>1173; 9908</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 7372</t>
+          <t>0; 8127</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7280; 13663</t>
+          <t>7246; 14248</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1062; 8661</t>
+          <t>1069; 8535</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1175; 10304</t>
+          <t>1181; 9354</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>955; 9844</t>
+          <t>1372; 10835</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11956; 20720</t>
+          <t>12405; 22261</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>3043</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5149</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>8331</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1105; 6811</t>
+          <t>1116; 6787</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3056,47 +3056,47 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1475; 5361</t>
+          <t>1033; 5077</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3953</t>
+          <t>0; 4923</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1992; 10514</t>
+          <t>1968; 10262</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 7251</t>
+          <t>0; 6994</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3109; 7436</t>
+          <t>3356; 8117</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4384</t>
+          <t>0; 4202</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4269; 14874</t>
+          <t>4222; 14880</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 6852</t>
+          <t>0; 7179</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5312; 11269</t>
+          <t>5275; 11265</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3195</t>
+          <t>3207</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>12001</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>15093</t>
+          <t>15208</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1070; 8549</t>
+          <t>1087; 9604</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1443; 5722</t>
+          <t>1572; 5776</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2041; 9480</t>
+          <t>2071; 10416</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8738; 15076</t>
+          <t>9040; 15551</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5229; 15739</t>
+          <t>4314; 15886</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11235; 19268</t>
+          <t>11825; 19320</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3674</t>
+          <t>5090</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>13550</t>
+          <t>16060</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>17225</t>
+          <t>21150</t>
         </is>
       </c>
     </row>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4985</t>
+          <t>0; 4849</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3472,47 +3472,47 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1129; 8575</t>
+          <t>1768; 10392</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 5985</t>
+          <t>0; 4786</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2160; 12534</t>
+          <t>2895; 13045</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1216; 10489</t>
+          <t>1237; 11304</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>9197; 18966</t>
+          <t>10994; 22470</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 5366</t>
+          <t>0; 4673</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3245; 14819</t>
+          <t>3214; 13677</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1219; 10609</t>
+          <t>1202; 11317</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>12072; 23603</t>
+          <t>14831; 28910</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1798</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>10300</t>
+          <t>12277</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>12099</t>
+          <t>14300</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 4081</t>
+          <t>0; 4255</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3675,52 +3675,52 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 4186</t>
+          <t>0; 4436</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>575; 4726</t>
+          <t>648; 5326</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>919; 8824</t>
+          <t>902; 8480</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2131; 11157</t>
+          <t>2118; 11232</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 7259</t>
+          <t>0; 6042</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>6483; 15232</t>
+          <t>7651; 18353</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1136; 9455</t>
+          <t>1144; 9905</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2104; 12263</t>
+          <t>2084; 11137</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0; 7078</t>
+          <t>0; 7891</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>8184; 17346</t>
+          <t>9116; 20584</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28548</t>
+          <t>30736</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>80752</t>
+          <t>86848</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>109300</t>
+          <t>117584</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0; 4547</t>
+          <t>0; 4266</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>6158; 20445</t>
+          <t>6405; 19858</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2442; 11524</t>
+          <t>2430; 11702</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22056; 37927</t>
+          <t>23183; 40028</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>4420; 17722</t>
+          <t>4599; 17041</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>39457; 67023</t>
+          <t>39427; 66518</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10177; 29027</t>
+          <t>9908; 28902</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>69568; 92229</t>
+          <t>76206; 98127</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5392; 19014</t>
+          <t>4675; 18213</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>49252; 79016</t>
+          <t>50132; 80908</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14368; 33654</t>
+          <t>14812; 35603</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>96424; 123491</t>
+          <t>104581; 133084</t>
         </is>
       </c>
     </row>
